--- a/deliverables/Afillar_API_vs_Platform_Mapping_v1.2.xlsx
+++ b/deliverables/Afillar_API_vs_Platform_Mapping_v1.2.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Call Map'!$A$1:$N$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Platform Requests'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Call Map'!$A$1:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Platform Requests'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'What We Add'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PA001 vs UP'!$A$1:$D$6</definedName>
   </definedNames>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Quotation, Tables</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1606,112 +1606,184 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Read plan, benefit, rule and insurer rows</t>
+          <t>Platform quotation validation (same gate as PA001 Get Plans)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Quotation</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>getDataTableByName</t>
+          <t>validate (gate)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
+          <t>SDK QuotationSdkClient.quotationApi().newValidateRequestBuilder().eventCode("").langId("").requestBody(copy of the request)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>dataTableName = UP_ table name</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>(no body)</t>
+          <t>&lt;the Get Plans request body as received, after our own validation&gt;</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>All rows of the table</t>
+          <t>none used; a rejection stops the request (400 UP-PLATFORM-VALIDATION or the platform 400)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>GetPlansPlatformValidate = Y (MC: Y)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Builds the plan list from the tables; no proposal or rating call. Age, term, premium mode and insurer checks.</t>
+          <t>Our own checks run first; the platform then validates code tables, data dictionary and rules. Result unused; a rejection stops the quote.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>UPGetPlans</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>/up/get-plans</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Read plan, benefit, rule and insurer rows</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>getDataTableByName</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>dataTableName = UP_ table name</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>All rows of the table</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Builds the plan list from the tables; no rating call. Age, term, premium mode and insurer checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>UPProposal</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>/up/proposal</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Create the proposal</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>application (create proposal)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>SDK ProposalSdkClient.proposalApi().newApplicationRequestBuilder().requestBody(payload)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>{
   "ApplicationNo": "&lt;applicationNo&gt;",
@@ -1778,74 +1850,74 @@
 }</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Created proposal (ProposalNo, PolicyId, premium after platform rating)</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Field-rule validation, drops PlanList and DuePremium (platform rating decides them), strips server-owned fields, defaults OrgCode, flattens payment info, stamps AgentCode (maker id).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>UPProposal</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>/up/proposal</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Alert the Proposal Checkers (SUBMITTED)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -1857,70 +1929,70 @@
 }</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>NotifyMode = LIVE; recorded as DRYRUN otherwise</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>UPProposal</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>/up/proposal</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Alert the Proposal Checkers (SUBMITTED)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -1930,89 +2002,17 @@
 }</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>NotifyMode = LIVE; recorded as DRYRUN otherwise</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>UPUpdateProposal</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>/up/update-proposal</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Load the stored proposal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>404 when missing, channel / product / open-state checks, creator check.</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2027,45 +2027,117 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Load the stored proposal</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>404 when missing, channel / product / open-state checks, creator check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>UPUpdateProposal</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>/up/update-proposal</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Save</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>save (update proposal)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newSaveRequestBuilder().requestBody(payload)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>{
   "ApplicationNo": "&lt;applicationNo&gt;",
@@ -2136,113 +2208,41 @@
 }</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Saved proposal (calculated plan row dropped by the platform)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Copies PolicyId, PolicyElementId, VersionSeq and the stored AgentCode into the payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>UPUpdateProposal</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>/up/update-proposal</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Recalculate</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>persistCalculate</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newPersistCalculateRequestBuilder().requestBody(policy)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>&lt;the save response (update-proposal) or the stored proposal (issue with Recalculate = Y)&gt;</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Proposal with premium factors recalculated and persisted</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>The platform save drops the calculated plan row, so premium is recalculated and persisted.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>UPIssue</t>
+          <t>UPUpdateProposal</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>/up/issue</t>
+          <t>/up/update-proposal</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Load the proposal</t>
+          <t>Recalculate</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2252,37 +2252,37 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>load</t>
+          <t>persistCalculate</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+          <t>SDK proposalApi().newPersistCalculateRequestBuilder().requestBody(policy)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>(no body)</t>
+          <t>&lt;the save response (update-proposal) or the stored proposal (issue with Recalculate = Y)&gt;</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+          <t>Proposal with premium factors recalculated and persisted</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>404, channel, product match, open-state and maker-checker checks.</t>
+          <t>The platform save drops the calculated plan row, so premium is recalculated and persisted.</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Recalculate</t>
+          <t>Load the proposal</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2324,47 +2324,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>persistCalculate</t>
+          <t>load</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SDK proposalApi().newPersistCalculateRequestBuilder().requestBody(policy)</t>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>&lt;the save response (update-proposal) or the stored proposal (issue with Recalculate = Y)&gt;</t>
+          <t>(no body)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Proposal with premium factors recalculated and persisted</t>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>only when Recalculate = Y is sent</t>
+          <t>always</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Optional, not part of the public contract.</t>
+          <t>404, channel, product match, open-state and maker-checker checks.</t>
         </is>
       </c>
     </row>
@@ -2381,119 +2381,191 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Recalculate</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>persistCalculate</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newPersistCalculateRequestBuilder().requestBody(policy)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>R04</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>&lt;the save response (update-proposal) or the stored proposal (issue with Recalculate = Y)&gt;</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Proposal with premium factors recalculated and persisted</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>only when Recalculate = Y is sent</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Optional, not part of the public contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>UPIssue</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>/up/issue</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>issuePolicy</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newIssuePolicyRequestBuilder().requestBody(map)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>{
   "ProposalNo": "&lt;ProposalNo&gt;"
 }</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Policy with PolicyNo</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Shapes the policy (commission switch, insurer).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>UPIssue</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>/up/issue</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Alert maker and customer</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -2505,70 +2577,70 @@
 }</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>LIVE only (DRYRUN otherwise)</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>UPIssue</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>/up/issue</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Alert maker and customer</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -2578,99 +2650,27 @@
 }</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>LIVE only (DRYRUN otherwise)</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>UPLoadPolicy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>/up/load-policy</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Load by policyNo or proposalNo</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Channel check, commission removed, payment info rebuilt, insurer added.</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>UPProposalReject</t>
+          <t>UPLoadPolicy</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>/up/proposal-reject</t>
+          <t>/up/load-policy</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Load the proposal</t>
+          <t>Load by policyNo or proposalNo</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>404, channel, product match, open state.</t>
+          <t>Channel check, commission removed, payment info rebuilt, insurer added.</t>
         </is>
       </c>
     </row>
@@ -2747,45 +2747,117 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Load the proposal</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>404, channel, product match, open state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>UPProposalReject</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>/up/proposal-reject</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Proposal</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>reject</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newRejectRequestBuilder().rejectVo(RejectVo)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>{
   "ProposalNo": "&lt;ProposalNo&gt;",
@@ -2793,74 +2865,74 @@
 }</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>none used (our reply is {status, message})</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Reason required (field rule).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>UPProposalReject</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>/up/proposal-reject</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Alert the maker</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -2872,70 +2944,70 @@
 }</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>LIVE only (DRYRUN otherwise)</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>UPProposalReject</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>/up/proposal-reject</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Alert the maker</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -2945,89 +3017,17 @@
 }</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>LIVE only (DRYRUN otherwise)</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>UPDocGeneration</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>/up/doc_generation</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Load the policy or proposal</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Channel check.</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3042,45 +3042,117 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Load the policy or proposal</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Channel check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>UPDocGeneration</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>/up/doc_generation</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Generate the PDF</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>printtask generate</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>REST https://portal-gw.insuremo.com/mo-fo/1.0/print/v3/printtask/generate (headers: Authorization Bearer &lt;caller token&gt;, x-mo-tenant-id)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>{
   "template_name": "&lt;UP_DocTemplate.TemplateName&gt;",
@@ -3092,91 +3164,19 @@
 }</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>data.target_file_content (base64 PDF)</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>unless PreviewData = Y</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Template from UP_DocTemplate, bilingual print data from UPDocBuilder, print host must be in AllowedHosts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>UPApplicationDocGeneration</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>/up/application_doc_generation</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Load the proposal</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Channel check.</t>
         </is>
       </c>
     </row>
@@ -3193,45 +3193,117 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Load the proposal</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Channel check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>UPApplicationDocGeneration</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>/up/application_doc_generation</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Generate the PDF</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>printtask generate</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>REST https://portal-gw.insuremo.com/mo-fo/1.0/print/v3/printtask/generate (headers: Authorization Bearer &lt;caller token&gt;, x-mo-tenant-id)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>{
   "template_name": "&lt;UP_DocTemplate.TemplateName&gt;",
@@ -3243,91 +3315,19 @@
 }</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>data.target_file_content (base64 PDF)</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>unless PreviewData = Y</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Same as UPDocGeneration with DocType Application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>UPCancelCheck</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>/up/cancel-check</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Load the policy (by policyNo, or by proposalNo then policyNo)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Must be issued, in force and enabled for the API.</t>
         </is>
       </c>
     </row>
@@ -3344,22 +3344,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Get the signed policy id</t>
+          <t>Load the policy (by policyNo, or by proposalNo then policyNo)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Proposal (REST)</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>load with signed policy id</t>
+          <t>load</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>policyNo</t>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>The endorsement service needs the id with its signature.</t>
+          <t>Must be issued, in force and enabled for the API.</t>
         </is>
       </c>
     </row>
@@ -3416,22 +3416,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Find an open request</t>
+          <t>Get the signed policy id</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Endorsement</t>
+          <t>Proposal (REST)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>queryPendingEndo</t>
+          <t>load with signed policy id</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3441,17 +3441,17 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
+          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>policyId (signed, sent once-encoded)</t>
+          <t>policyNo</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
+          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Another kind of pending endorsement blocks the request (409); an existing cancellation is shown again.</t>
+          <t>The endorsement service needs the id with its signature.</t>
         </is>
       </c>
     </row>
@@ -3488,45 +3488,117 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Find an open request</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>queryPendingEndo</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>policyId (signed, sent once-encoded)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Another kind of pending endorsement blocks the request (409); an existing cancellation is shown again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>UPCancelCheck</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>/up/cancel-check</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Create the pending request</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Endorsement</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>createEx</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>REST /platform/endo/core/endo/v1/createEx</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>{
   "EndoEffectiveDate": "&lt;policy start (free look) or the cancellation date&gt;",
@@ -3547,74 +3619,74 @@
 }</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>The endorsement (EndoNo, EndoId, NewPolicy); on approval it is the body of calculateEx</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>no pending request exists</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>The refund is calculated in our code (free look 100%, then pro-rata x 80%); the platform calculates none.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>UPCancelCheck</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>/up/cancel-check</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Alert the Cancellation Checkers</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -3626,70 +3698,70 @@
 }</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>new request; LIVE only</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>UPCancelCheck</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>/up/cancel-check</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Alert the Cancellation Checkers</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -3699,89 +3771,17 @@
 }</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>new request; LIVE only</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>UPCancelApprove</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>/up/cancel-approve</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Load the policy</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Channel and product checks.</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3796,22 +3796,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Get the signed policy id</t>
+          <t>Load the policy</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Proposal (REST)</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>load with signed policy id</t>
+          <t>load</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>policyNo</t>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3849,7 +3849,11 @@
           <t>always</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Channel and product checks.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3864,22 +3868,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Find the pending request</t>
+          <t>Get the signed policy id</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Endorsement</t>
+          <t>Proposal (REST)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>queryPendingEndo</t>
+          <t>load with signed policy id</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3889,17 +3893,17 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
+          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>policyId (signed, sent once-encoded)</t>
+          <t>policyNo</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
+          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3917,11 +3921,7 @@
           <t>always</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>RequestNo must match (404 otherwise); requester must not be the caller.</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Withdraw the saved request</t>
+          <t>Find the pending request</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3951,27 +3951,27 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>suspendEndorsement</t>
+          <t>queryPendingEndo</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/suspendEndorsement?endoId=&lt;EndoId&gt;</t>
+          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>endoId</t>
+          <t>policyId (signed, sent once-encoded)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -3981,15 +3981,19 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200 / 204</t>
+          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>always (reject, and first step of approve)</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>RequestNo must match (404 otherwise); requester must not be the caller.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4004,45 +4008,113 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Withdraw the saved request</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>suspendEndorsement</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>REST /platform/endo/core/endo/v1/suspendEndorsement?endoId=&lt;EndoId&gt;</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>endoId</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 200 / 204</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>always (reject, and first step of approve)</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>UPCancelApprove</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>/up/cancel-approve</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Create a fresh endorsement</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Endorsement</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>createEx</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>REST /platform/endo/core/endo/v1/createEx</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>{
   "EndoEffectiveDate": "&lt;policy start (free look) or the cancellation date&gt;",
@@ -4063,89 +4135,21 @@
 }</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>The endorsement (EndoNo, EndoId, NewPolicy); on approval it is the body of calculateEx</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Decision = APPROVE</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Saved request is thin: calculateEx needs the full new policy that only createEx returns.</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>UPCancelApprove</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>/up/cancel-approve</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Calculate</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Endorsement</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>calculateEx</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>REST /platform/endo/core/endo/v1/calculateEx</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>&lt;the createEx response of the fresh endorsement&gt;</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Calculated endorsement (body of validate and issueEndorsement)</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Decision = APPROVE</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4160,12 +4164,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Validate</t>
+          <t>Calculate</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4175,7 +4179,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>validate</t>
+          <t>calculateEx</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4185,7 +4189,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/validate</t>
+          <t>REST /platform/endo/core/endo/v1/calculateEx</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4195,17 +4199,17 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>&lt;the calculateEx response&gt;</t>
+          <t>&lt;the createEx response of the fresh endorsement&gt;</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200 / 204 = valid; OrgCode is checked against code table PubBranch</t>
+          <t>Calculated endorsement (body of validate and issueEndorsement)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4213,11 +4217,7 @@
           <t>Decision = APPROVE</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>A platform refusal becomes HTTP 409 with the new request left pending.</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Issue the endorsement</t>
+          <t>Validate</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>issueEndorsement</t>
+          <t>validate</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/issueEndorsement</t>
+          <t>REST /platform/endo/core/endo/v1/validate</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; the policy becomes Cancelled</t>
+          <t>HTTP 200 / 204 = valid; OrgCode is checked against code table PubBranch</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>The policy becomes Cancelled.</t>
+          <t>A platform refusal becomes HTTP 409 with the new request left pending.</t>
         </is>
       </c>
     </row>
@@ -4304,52 +4304,52 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Load the policy again</t>
+          <t>Issue the endorsement</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Endorsement</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>load</t>
+          <t>issueEndorsement</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+          <t>REST /platform/endo/core/endo/v1/issueEndorsement</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>(no body)</t>
+          <t>&lt;the calculateEx response&gt;</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+          <t>HTTP 200; the policy becomes Cancelled</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Returns the new status.</t>
+          <t>The policy becomes Cancelled.</t>
         </is>
       </c>
     </row>
@@ -4376,45 +4376,117 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Load the policy again</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Decision = APPROVE</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Returns the new status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>UPCancelApprove</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>/up/cancel-approve</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Alert maker and customer</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -4426,70 +4498,70 @@
 }</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>LIVE only</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>UPCancelApprove</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>/up/cancel-approve</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Alert maker and customer</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -4499,82 +4571,14 @@
 }</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>LIVE only</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>UPCancelDetail</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>/up/cancel-detail</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Load the policy</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -4592,22 +4596,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Get the signed policy id</t>
+          <t>Load the policy</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Proposal (REST)</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>load with signed policy id</t>
+          <t>load</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4617,17 +4621,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>policyNo</t>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -4637,7 +4641,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -4660,22 +4664,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Read the pending request</t>
+          <t>Get the signed policy id</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Endorsement</t>
+          <t>Proposal (REST)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>queryPendingEndo</t>
+          <t>load with signed policy id</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4685,17 +4689,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
+          <t>REST /platform/proposal/v1/load?policyNo=&lt;PolicyNo&gt;</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>policyId (signed, sent once-encoded)</t>
+          <t>policyNo</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -4705,7 +4709,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
+          <t>PolicyId in the form &lt;id&gt;,&lt;signature&gt;</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4713,41 +4717,37 @@
           <t>always</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>Shows requester, reason, refund calculation and CanDecide; creates nothing.</t>
-        </is>
-      </c>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>UPListMasterTable</t>
+          <t>UPCancelDetail</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/up/list-master-table</t>
+          <t>/up/cancel-detail</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Read the table</t>
+          <t>Read the pending request</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Endorsement</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>getDataTableByName</t>
+          <t>queryPendingEndo</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -4757,17 +4757,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
+          <t>REST /platform/endo/core/endo/v1/queryPendingEndo?policyId=&lt;signed id&gt;</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>dataTableName = UP_ table name</t>
+          <t>policyId (signed, sent once-encoded)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>All rows of the table</t>
+          <t>Pending endorsement (EndoNo, EndoId, EndoType, CancelType, OtherCancelReason, EndoEffectiveDate, DataEntryUserId, InsertTime) or empty</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -4787,19 +4787,19 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Only tables listed in MasterTables; commission column removed.</t>
+          <t>Shows requester, reason, refund calculation and CanDecide; creates nothing.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>UPCommissionQuery</t>
+          <t>UPListMasterTable</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/up/commission-query</t>
+          <t>/up/list-master-table</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>By policy: load</t>
+          <t>Read the table</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Proposal</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>load</t>
+          <t>getDataTableByName</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4829,17 +4829,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+          <t>dataTableName = UP_ table name</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -4849,17 +4849,17 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+          <t>All rows of the table</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>PolicyNo sent</t>
+          <t>always</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Commission shown only by this API.</t>
+          <t>Only tables listed in MasterTables; commission column removed.</t>
         </is>
       </c>
     </row>
@@ -4876,45 +4876,117 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>By policy: load</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>PolicyNo sent</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Commission shown only by this API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>UPCommissionQuery</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>/up/commission-query</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>By period: search issued policies</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>queryPolicy (policy index)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newQueryPolicyRequestBuilder().searchCondition(sc) ; REST path /platform/proposal/v1/queryPolicy</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -4936,91 +5008,19 @@
 }</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Total and EsDocs (PolicyNo, ProposalNo, ProposalStatus, PolicyStatus, ProductCode, dates; premium is 0 in the index)</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>FromDate / ToDate sent</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Page totals; the index holds no premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>UPCommissionQuery</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>/up/commission-query</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>By period: load every hit</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>FromDate / ToDate sent</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Channel filter; premium and commission read from the policy.</t>
         </is>
       </c>
     </row>
@@ -5037,22 +5037,22 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>By configuration: read plan rows</t>
+          <t>By period: load every hit</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Proposal</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>getDataTableByName</t>
+          <t>load</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>dataTableName = UP_ table name</t>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -5082,72 +5082,144 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>All rows of the table</t>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>ProductCode without dates</t>
+          <t>FromDate / ToDate sent</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>No platform call except the tables.</t>
+          <t>Channel filter; premium and commission read from the policy.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>UPCommissionQuery</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>/up/commission-query</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>By configuration: read plan rows</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>getDataTableByName</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>dataTableName = UP_ table name</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>All rows of the table</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>ProductCode without dates</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>No platform call except the tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>UPFeedFile</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>/up/generate-feedfile</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Search policies</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>queryPolicy (policy index)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newQueryPolicyRequestBuilder().searchCondition(sc) ; REST path /platform/proposal/v1/queryPolicy</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5169,146 +5241,146 @@
 }</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Total and EsDocs (PolicyNo, ProposalNo, ProposalStatus, PolicyStatus, ProductCode, dates; premium is 0 in the index)</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>always</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>Capped by FeedMaxRecords / FeedMaxPages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>UPFeedFile</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>/up/generate-feedfile</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Load every hit</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Columns from UP_FeedColumn; Excel or JSON output.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>UPFeedFile</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>/up/generate-feedfile</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Load every hit</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Columns from UP_FeedColumn; Excel or JSON output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>UPWorklistApi</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>/up/worklist</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Proposal queue: search per product</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>queryPolicy (policy index)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newQueryPolicyRequestBuilder().searchCondition(sc) ; REST path /platform/proposal/v1/queryPolicy</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5330,91 +5402,19 @@
 }</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Total and EsDocs (PolicyNo, ProposalNo, ProposalStatus, PolicyStatus, ProductCode, dates; premium is 0 in the index)</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Type PROPOSAL or MINE</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>Status, dates; MINE adds AgentCode = caller. Merged and paged in our code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>UPWorklistApi</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>/up/worklist</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Proposal queue: load each row shown</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Type PROPOSAL or MINE</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Maker name, plan, premium, reject reason.</t>
         </is>
       </c>
     </row>
@@ -5431,45 +5431,117 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Proposal queue: load each row shown</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Type PROPOSAL or MINE</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Maker name, plan, premium, reject reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>UPWorklistApi</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>/up/worklist</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Cancellation queue: endorsement search per product</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>endorsement query</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>REST /platform/endo/v1/query (via UPPlatformClient.call)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5487,142 +5559,142 @@
 }</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>QueryResult.Results[].EsDocs (EndoNo, PolicyNo, EndoStatus, EndoEffectiveDate, FirstDataEntryDate)</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Type CANCELLATION</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>Only PENDING and ISSUED can be listed.</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>UPWorklistApi</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>/up/worklist</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Cancellation queue: load each row shown</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Type CANCELLATION</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>UPWorklistApi</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>/up/worklist</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation queue: load each row shown</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Type CANCELLATION</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>UPDashboard</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>/up/dashboard</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>SUMMARY: policy searches (about 4 per product)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>queryPolicy (policy index)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newQueryPolicyRequestBuilder().searchCondition(sc) ; REST path /platform/proposal/v1/queryPolicy</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5644,74 +5716,74 @@
 }</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Total and EsDocs (PolicyNo, ProposalNo, ProposalStatus, PolicyStatus, ProductCode, dates; premium is 0 in the index)</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Section SUMMARY</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>Counts only (PageSize 1).</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>UPDashboard</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>/up/dashboard</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>SUMMARY: endorsement searches (2 per product)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>endorsement query</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>REST /platform/endo/v1/query (via UPPlatformClient.call)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5729,74 +5801,74 @@
 }</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>QueryResult.Results[].EsDocs (EndoNo, PolicyNo, EndoStatus, EndoEffectiveDate, FirstDataEntryDate)</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Section SUMMARY</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>Pending and issued cancellations.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>UPDashboard</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>/up/dashboard</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>COMMISSION: search issued policies of one product</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>queryPolicy (policy index)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SDK proposalApi().newQueryPolicyRequestBuilder().searchCondition(sc) ; REST path /platform/proposal/v1/queryPolicy</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>{
   "Conditions": {
@@ -5818,113 +5890,41 @@
 }</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Total and EsDocs (PolicyNo, ProposalNo, ProposalStatus, PolicyStatus, ProductCode, dates; premium is 0 in the index)</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>Section COMMISSION</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>Up to DashboardMaxPolicies (60).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>UPDashboard</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>/up/dashboard</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>COMMISSION: load each policy</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Proposal</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>load</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>(no body)</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Section COMMISSION</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>Premium and commission per policy, by plan.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>UPShare</t>
+          <t>UPDashboard</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/up/share</t>
+          <t>/up/dashboard</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Load the proposal / policy</t>
+          <t>COMMISSION: load each policy</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>DocType PROPOSAL or POLICY</t>
+          <t>Section COMMISSION</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Channel check; contact from the request or the stored record.</t>
+          <t>Premium and commission per policy, by plan.</t>
         </is>
       </c>
     </row>
@@ -5991,45 +5991,117 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Load the proposal / policy</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Proposal</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SDK proposalApi().newLoadRequestBuilder().proposalNo(x) | .policyNo(x) .withCodeDesc(Y)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>proposalNo or policyNo; withCodeDesc = TrueValue (Y)</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>(no body)</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Full stored proposal / policy (including masked and encrypted TempData)</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>DocType PROPOSAL or POLICY</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Channel check; contact from the request or the stored record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>UPShare</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>/up/share</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Send email</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>send email</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SDK SnsSdkClient.emailApi().newSendEmailRequestBuilder().requestBody(SendEmailRequest)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>{
   "to": [
@@ -6041,70 +6113,70 @@
 }</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>none used (result row SENT / FAILED)</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Channel EMAIL or BOTH; LIVE only</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>UPShare</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>/up/share</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Send SMS</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>send SMS</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SDK smsApi().newSendSmsRequestBuilder().requestBody(SendSMSRequest)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>{
   "to": "&lt;mobile&gt;",
@@ -6114,20 +6186,20 @@
 }</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>none used</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Channel SMS or BOTH; LIVE only</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N60"/>
+  <autoFilter ref="A1:N61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6138,7 +6210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7342,57 +7414,109 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Quotation</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>validate (gate)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>SDK QuotationSdkClient.quotationApi().newValidateRequestBuilder().eventCode("").langId("").requestBody(copy of the request)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>&lt;the Get Plans request body as received, after our own validation&gt;</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>GetPlansPlatformValidate (Y = on)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>UPGetPlans.groovy</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>none used; a rejection stops the request (400 UP-PLATFORM-VALIDATION or the platform 400)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>R19</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>getDataTableByName</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>SDK TablesSdkClient.dataTableApi().newGetDataTableByNameRequestBuilder().dataTableConditionVo(vo)</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>dataTableName = UP_ table name</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>(no body)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>UPDataUtil.readRecords (read once per request and cached)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>All rows of the table</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7453,12 +7577,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Platform has quotation and rating services.</t>
+          <t>Platform has quotation and rating services; PA001 runs the quotation validate then an adapter call.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>No platform call: plans and premiums come from the UP_ tables, so Get Plans is fast and the premium equals the one the rating gives later.</t>
+          <t>Runs the same platform quotation validation as PA001 (switch GetPlansPlatformValidate), then builds plans and premiums from the UP_ tables with no rating call, so the premium equals the one the rating gives later.</t>
         </is>
       </c>
     </row>
